--- a/data/chinese/P3T1_Chapter3.xlsx
+++ b/data/chinese/P3T1_Chapter3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B05030-A352-6444-8D5C-D87D79EB70CB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57870B12-7AE5-6445-BFB8-6A955ADCE435}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,14 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暫沒有需記認寫生字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暫沒有必懂寫生字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>火柴</t>
   </si>
   <si>
@@ -140,6 +132,52 @@
   </si>
   <si>
     <t>以前人們會用火柴點燃蠟燭。</t>
+  </si>
+  <si>
+    <t>就是夢，睡覺時腦裡出現的畫面。</t>
+  </si>
+  <si>
+    <t>夢兒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝴蝶飛進我的夢兒。</t>
+  </si>
+  <si>
+    <t>擋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮住、阻礙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大樹的枝葉擋住了刺眼的陽光。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颳風又下雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小草勇敢地抵抗冰冷的風雪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>從當中挑取合適的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老師請大家選出班長。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -226,7 +264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -247,9 +285,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,13 +602,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -582,13 +617,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -597,13 +632,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -612,13 +647,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -627,13 +662,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -642,13 +677,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -657,13 +692,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -672,13 +707,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -688,13 +723,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -906,14 +941,14 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>7</v>
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -921,24 +956,48 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="27">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="27">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="27">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="27">
